--- a/Analiza_preferencji_szamponow_komplet_36.xlsx
+++ b/Analiza_preferencji_szamponow_komplet_36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -275,109 +275,103 @@
     <t>Keratyna (+8 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
   </si>
   <si>
-    <t>Bez SLS / SLES (+6 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Olejki – arganowy, kokosowy (+7 zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);Olejki – arganowy, kokosowy (+7 zł);Keratyna (+8 zł);</t>
+    <t>Działanie: regeneracja zniszczonych włosów (+6 zł);Marka fryzjerska (+8zł);Naturalne / roślinne składniki (+12 zł);</t>
+  </si>
+  <si>
+    <t>Bez SLS / SLES (+6 zł);Keratyna (+8 zł);</t>
+  </si>
+  <si>
+    <t>Certyfikat vegan / cruelty-free (+9 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Olejki – arganowy, kokosowy (+7 zł);</t>
+  </si>
+  <si>
+    <t>Keratyna (+8 zł);Marka fryzjerska (+8zł);Format: szampon w kostce (+5 zł);</t>
+  </si>
+  <si>
+    <t>Naturalne / roślinne składniki (+12 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Keratyna (+8 zł);</t>
+  </si>
+  <si>
+    <t>Naturalne / roślinne składniki (+12 zł);Marka fryzjerska (+8zł);Działanie: regeneracja zniszczonych włosów (+6 zł);</t>
+  </si>
+  <si>
+    <t>Marka fryzjerska (+8zł);Keratyna (+8 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
+  </si>
+  <si>
+    <t>Format: szampon w kostce (+5 zł);Keratyna (+8 zł);</t>
+  </si>
+  <si>
+    <t>Marka fryzjerska (+8zł);Format: szampon w kostce (+5 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);</t>
   </si>
   <si>
     <t>Format: szampon w kostce (+5 zł);</t>
   </si>
   <si>
-    <t>Działanie: regeneracja zniszczonych włosów (+6 zł);Bez SLS / SLES (+6 zł);Keratyna (+8 zł);</t>
-  </si>
-  <si>
-    <t>Olejki – arganowy, kokosowy (+7 zł);Keratyna (+8 zł);Bez SLS / SLES (+6 zł);</t>
-  </si>
-  <si>
-    <t>Marka fryzjerska (+8zł);Olejki – arganowy, kokosowy (+7 zł);Format: szampon w kostce (+5 zł);</t>
+    <t>Bez SLS / SLES (+6 zł);Naturalne / roślinne składniki (+12 zł);Marka fryzjerska (+8zł);</t>
+  </si>
+  <si>
+    <t>Olejki – arganowy, kokosowy (+7 zł);</t>
+  </si>
+  <si>
+    <t>Certyfikat vegan / cruelty-free (+9 zł);Marka fryzjerska (+8zł);</t>
+  </si>
+  <si>
+    <t>Certyfikat vegan / cruelty-free (+9 zł);Olejki – arganowy, kokosowy (+7 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);</t>
+  </si>
+  <si>
+    <t>Naturalne / roślinne składniki (+12 zł);</t>
+  </si>
+  <si>
+    <t>Marka fryzjerska (+8zł);Keratyna (+8 zł);Format: szampon w kostce (+5 zł);</t>
+  </si>
+  <si>
+    <t>Działanie: regeneracja zniszczonych włosów (+6 zł);Naturalne / roślinne składniki (+12 zł);</t>
+  </si>
+  <si>
+    <t>Działanie: regeneracja zniszczonych włosów (+6 zł);Olejki – arganowy, kokosowy (+7 zł);Marka fryzjerska (+8zł);</t>
+  </si>
+  <si>
+    <t>Format: szampon w kostce (+5 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Marka fryzjerska (+8zł);</t>
+  </si>
+  <si>
+    <t>Olejki – arganowy, kokosowy (+7 zł);Marka fryzjerska (+8zł);</t>
+  </si>
+  <si>
+    <t>Keratyna (+8 zł);Marka fryzjerska (+8zł);</t>
+  </si>
+  <si>
+    <t>Certyfikat vegan / cruelty-free (+9 zł);Naturalne / roślinne składniki (+12 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);</t>
+  </si>
+  <si>
+    <t>Bez SLS / SLES (+6 zł);</t>
+  </si>
+  <si>
+    <t>Olejki – arganowy, kokosowy (+7 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Keratyna (+8 zł);Naturalne / roślinne składniki (+12 zł);</t>
+  </si>
+  <si>
+    <t>Bez SLS / SLES (+6 zł);Format: szampon w kostce (+5 zł);Keratyna (+8 zł);Marka fryzjerska (+8zł);</t>
+  </si>
+  <si>
+    <t>Bez SLS / SLES (+6 zł);Naturalne / roślinne składniki (+12 zł);</t>
+  </si>
+  <si>
+    <t>Naturalne / roślinne składniki (+12 zł);Olejki – arganowy, kokosowy (+7 zł);Bez SLS / SLES (+6 zł);</t>
+  </si>
+  <si>
+    <t>Olejki – arganowy, kokosowy (+7 zł);Bez SLS / SLES (+6 zł);Naturalne / roślinne składniki (+12 zł);</t>
+  </si>
+  <si>
+    <t>Naturalne / roślinne składniki (+12 zł);Bez SLS / SLES (+6 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
+  </si>
+  <si>
+    <t>Certyfikat vegan / cruelty-free (+9 zł);</t>
+  </si>
+  <si>
+    <t>Marka fryzjerska (+8zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Keratyna (+8 zł);</t>
+  </si>
+  <si>
+    <t>Naturalne / roślinne składniki (+12 zł);Olejki – arganowy, kokosowy (+7 zł);</t>
   </si>
   <si>
     <t>Keratyna (+8 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);</t>
-  </si>
-  <si>
-    <t>Marka fryzjerska (+8zł);Keratyna (+8 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);Keratyna (+8 zł);Naturalne / roślinne składniki (+12 zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);Marka fryzjerska (+8zł);Naturalne / roślinne składniki (+12 zł);</t>
-  </si>
-  <si>
-    <t>Olejki – arganowy, kokosowy (+7 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Keratyna (+8 zł);</t>
-  </si>
-  <si>
-    <t>Olejki – arganowy, kokosowy (+7 zł);</t>
-  </si>
-  <si>
-    <t>Olejki – arganowy, kokosowy (+7 zł);Format: szampon w kostce (+5 zł);</t>
-  </si>
-  <si>
-    <t>Format: szampon w kostce (+5 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
-  </si>
-  <si>
-    <t>Naturalne / roślinne składniki (+12 zł);Keratyna (+8 zł);</t>
-  </si>
-  <si>
-    <t>Olejki – arganowy, kokosowy (+7 zł);Bez SLS / SLES (+6 zł);Keratyna (+8 zł);</t>
-  </si>
-  <si>
-    <t>Keratyna (+8 zł);Marka fryzjerska (+8zł);Naturalne / roślinne składniki (+12 zł);</t>
-  </si>
-  <si>
-    <t>Naturalne / roślinne składniki (+12 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);Marka fryzjerska (+8zł);Keratyna (+8 zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Naturalne / roślinne składniki (+12 zł);</t>
-  </si>
-  <si>
-    <t>Certyfikat vegan / cruelty-free (+9 zł);Olejki – arganowy, kokosowy (+7 zł);Bez SLS / SLES (+6 zł);</t>
-  </si>
-  <si>
-    <t>Marka fryzjerska (+8zł);</t>
-  </si>
-  <si>
-    <t>Keratyna (+8 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
-  </si>
-  <si>
-    <t>Certyfikat vegan / cruelty-free (+9 zł);Naturalne / roślinne składniki (+12 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);</t>
-  </si>
-  <si>
-    <t>Olejki – arganowy, kokosowy (+7 zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Keratyna (+8 zł);Naturalne / roślinne składniki (+12 zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);Format: szampon w kostce (+5 zł);Keratyna (+8 zł);Marka fryzjerska (+8zł);</t>
-  </si>
-  <si>
-    <t>Bez SLS / SLES (+6 zł);Naturalne / roślinne składniki (+12 zł);</t>
-  </si>
-  <si>
-    <t>Naturalne / roślinne składniki (+12 zł);Olejki – arganowy, kokosowy (+7 zł);Bez SLS / SLES (+6 zł);</t>
-  </si>
-  <si>
-    <t>Olejki – arganowy, kokosowy (+7 zł);Bez SLS / SLES (+6 zł);Naturalne / roślinne składniki (+12 zł);</t>
-  </si>
-  <si>
-    <t>Naturalne / roślinne składniki (+12 zł);Bez SLS / SLES (+6 zł);Certyfikat vegan / cruelty-free (+9 zł);</t>
-  </si>
-  <si>
-    <t>Certyfikat vegan / cruelty-free (+9 zł);</t>
-  </si>
-  <si>
-    <t>Marka fryzjerska (+8zł);Działanie: regeneracja zniszczonych włosów (+6 zł);Keratyna (+8 zł);</t>
-  </si>
-  <si>
-    <t>Marka fryzjerska (+8zł);Bez SLS / SLES (+6 zł);Olejki – arganowy, kokosowy (+7 zł);</t>
-  </si>
-  <si>
-    <t>Działanie: regeneracja zniszczonych włosów (+6 zł);Olejki – arganowy, kokosowy (+7 zł);</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1121,7 @@
         <v>55</v>
       </c>
       <c r="X6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1195,7 +1189,7 @@
         <v>56</v>
       </c>
       <c r="X7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1263,7 +1257,7 @@
         <v>57</v>
       </c>
       <c r="X8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1331,7 +1325,7 @@
         <v>58</v>
       </c>
       <c r="X9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1399,7 +1393,7 @@
         <v>59</v>
       </c>
       <c r="X10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1467,7 +1461,7 @@
         <v>60</v>
       </c>
       <c r="X11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1535,7 +1529,7 @@
         <v>61</v>
       </c>
       <c r="X12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1597,7 +1591,7 @@
         <v>62</v>
       </c>
       <c r="X13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1665,7 +1659,7 @@
         <v>63</v>
       </c>
       <c r="X14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1733,7 +1727,7 @@
         <v>64</v>
       </c>
       <c r="X15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1801,7 +1795,7 @@
         <v>65</v>
       </c>
       <c r="X16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1869,7 +1863,7 @@
         <v>66</v>
       </c>
       <c r="X17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1937,7 +1931,7 @@
         <v>67</v>
       </c>
       <c r="X18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2005,7 +1999,7 @@
         <v>68</v>
       </c>
       <c r="X19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2073,7 +2067,7 @@
         <v>69</v>
       </c>
       <c r="X20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2141,7 +2135,7 @@
         <v>70</v>
       </c>
       <c r="X21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:24">
@@ -2206,7 +2200,7 @@
         <v>71</v>
       </c>
       <c r="X22" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2274,7 +2268,7 @@
         <v>72</v>
       </c>
       <c r="X23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2342,7 +2336,7 @@
         <v>73</v>
       </c>
       <c r="X24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2410,7 +2404,7 @@
         <v>74</v>
       </c>
       <c r="X25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:24">
@@ -2478,7 +2472,7 @@
         <v>75</v>
       </c>
       <c r="X26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2546,7 +2540,7 @@
         <v>76</v>
       </c>
       <c r="X27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -2608,7 +2602,7 @@
         <v>77</v>
       </c>
       <c r="X28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2676,7 +2670,7 @@
         <v>78</v>
       </c>
       <c r="X29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -2741,7 +2735,7 @@
         <v>79</v>
       </c>
       <c r="X30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -2809,7 +2803,7 @@
         <v>80</v>
       </c>
       <c r="X31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:24">
@@ -2877,7 +2871,7 @@
         <v>81</v>
       </c>
       <c r="X32" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -2945,7 +2939,7 @@
         <v>82</v>
       </c>
       <c r="X33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:24">
@@ -3013,7 +3007,7 @@
         <v>83</v>
       </c>
       <c r="X34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:24">
@@ -3081,7 +3075,7 @@
         <v>84</v>
       </c>
       <c r="X35" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:24">
@@ -3146,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="X36" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:24">
@@ -3211,7 +3205,7 @@
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
